--- a/Owl/docs/工作报告26年第11周_崔永元.xlsx
+++ b/Owl/docs/工作报告26年第11周_崔永元.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871ED5CC-98FF-404E-A6AC-54EEBCEE9608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBCA135-A15B-472A-A500-1B15D9345D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,10 +35,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>今天工作内容</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>风险与问题</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -100,12 +96,6 @@
   </si>
   <si>
     <t>完成项目考点前三章的学习</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、远程协助验证demo基本物理检查；
-2、整理整机软件方案文体店，提供到项目经理处；
-3、与客户提前对接demo机验证流程</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -151,6 +141,16 @@
   </si>
   <si>
     <t>职业发展转换的要求，从技术岗转为技术型项目管理岗，弱化开发方面工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本周工作内容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、远程协助验证demo基本物理特性（气密性等）检查；
+2、整理整机软件方案问题，产出文件提供到项目经理处；
+3、与客户提前对接demo机验证流程</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -615,22 +615,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -642,59 +657,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1018,16 +1018,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
@@ -1040,204 +1040,204 @@
         <v>2</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="37"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="39"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="40"/>
+      <c r="A4" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="H5" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="6">
         <v>1</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
+      <c r="B6" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
       <c r="F6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="41">
+        <v>13</v>
+      </c>
+      <c r="G6" s="19">
         <v>46094</v>
       </c>
-      <c r="H6" s="43" t="s">
-        <v>22</v>
+      <c r="H6" s="21" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A7" s="6">
         <v>2</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
+      <c r="B7" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="41">
+        <v>13</v>
+      </c>
+      <c r="G7" s="19">
         <v>46105</v>
       </c>
-      <c r="H7" s="43" t="s">
-        <v>21</v>
+      <c r="H7" s="21" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" s="6">
         <v>3</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
+      <c r="B8" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
       <c r="F8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="41">
+        <v>13</v>
+      </c>
+      <c r="G8" s="19">
         <v>46094</v>
       </c>
-      <c r="H8" s="42" t="s">
-        <v>19</v>
+      <c r="H8" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>4</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
+      <c r="B9" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
       <c r="F9" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="41">
+        <v>13</v>
+      </c>
+      <c r="G9" s="19">
         <v>46188</v>
       </c>
-      <c r="H9" s="44" t="s">
-        <v>20</v>
+      <c r="H9" s="22" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="27"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A11" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="40"/>
+      <c r="A11" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="33"/>
+      <c r="F12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="H12" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="72.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>1</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="45"/>
+      <c r="E13" s="38"/>
       <c r="F13" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H13" s="18"/>
     </row>
@@ -1245,215 +1245,196 @@
       <c r="A14" s="4">
         <v>2</v>
       </c>
-      <c r="B14" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="45"/>
+      <c r="B14" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="38"/>
       <c r="F14" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="6"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" s="6"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="27"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A19" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
+      <c r="A19" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
       <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="H20" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A21" s="4">
         <v>1</v>
       </c>
-      <c r="B21" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
+      <c r="B21" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
       <c r="F21" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="41">
+        <v>13</v>
+      </c>
+      <c r="G21" s="19">
         <v>46142</v>
       </c>
-      <c r="H21" s="43" t="s">
-        <v>31</v>
+      <c r="H21" s="21" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A22" s="4">
         <v>2</v>
       </c>
-      <c r="B22" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
+      <c r="B22" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
       <c r="F22" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="41">
+        <v>13</v>
+      </c>
+      <c r="G22" s="19">
         <v>46132</v>
       </c>
-      <c r="H22" s="43" t="s">
-        <v>27</v>
+      <c r="H22" s="21" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A23" s="4">
         <v>3</v>
       </c>
-      <c r="B23" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
+      <c r="B23" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="41">
+        <v>13</v>
+      </c>
+      <c r="G23" s="19">
         <v>46157</v>
       </c>
-      <c r="H23" s="43" t="s">
-        <v>28</v>
+      <c r="H23" s="21" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A24" s="6"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="23"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="45"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A25" s="6"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="23"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="45"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="7"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A26" s="6"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="23"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="45"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="7"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="41"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A19:G19"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B17:C17"/>
@@ -1467,6 +1448,25 @@
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
